--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486922_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486922_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.443</v>
+        <v>7.4233</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7742</v>
+        <v>6.2585</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6688</v>
+        <v>1.1649</v>
       </c>
       <c r="G2" t="n">
         <v>5.9578</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0129</v>
+        <v>-0.0067</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0462</v>
+        <v>-0.5619</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0591</v>
+        <v>0.5552</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7905</v>
+        <v>3.2113</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1061</v>
+        <v>1.4083</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6844</v>
+        <v>1.803</v>
       </c>
       <c r="G3" t="n">
         <v>0.9517</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1613</v>
+        <v>0.2595</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2675</v>
+        <v>0.0347</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1063</v>
+        <v>0.2249</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3989</v>
+        <v>0.8648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4399</v>
+        <v>0.4425</v>
       </c>
       <c r="F4" t="n">
-        <v>0.959</v>
+        <v>0.4223</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2975</v>
+        <v>-0.2387</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07140000000000001</v>
+        <v>2.0664</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2261</v>
+        <v>-2.3051</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1303</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1065</v>
+        <v>2.1447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2368</v>
+        <v>-1.4476</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4278</v>
+        <v>-0.9358</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0351</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4629</v>
+        <v>-0.8575</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3125</v>
+        <v>0.0871</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0613</v>
+        <v>-0.2443</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2512</v>
+        <v>0.3314</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5893</v>
+        <v>2.2484</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4805</v>
+        <v>2.2484</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.7284</v>
+        <v>-0.265</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5374</v>
+        <v>1.0361</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.0998</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4186</v>
+        <v>-0.1818</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9866</v>
+        <v>0.2816</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8139</v>
+        <v>0.1573</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3835</v>
+        <v>0.0389</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1974</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2458</v>
+        <v>-0.0575</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0351</v>
+        <v>-0.2208</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2107</v>
+        <v>0.1632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1101</v>
+        <v>-0.3555</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3334</v>
+        <v>-0.4224</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4435</v>
+        <v>0.0669</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4637</v>
+        <v>0.7605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3379</v>
+        <v>-0.4356</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1259</v>
+        <v>1.1961</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2387</v>
+        <v>-0.2975</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0664</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3051</v>
+        <v>-0.2261</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.1303</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1447</v>
+        <v>-0.1065</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4476</v>
+        <v>0.2368</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9358</v>
+        <v>-0.4278</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0351</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8575</v>
+        <v>-0.4629</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.2321</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-2.2588</v>
       </c>
       <c r="R6" t="n">
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3139</v>
+        <v>0.6741</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3489</v>
+        <v>0.1857</v>
       </c>
       <c r="U6" t="n">
-        <v>0.035</v>
+        <v>0.4883</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2484</v>
+        <v>0.5893</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2484</v>
+        <v>0.4805</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3931</v>
+        <v>0.7053</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4355</v>
+        <v>-2.3875</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8286</v>
+        <v>3.0928</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0998</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1818</v>
+        <v>0.4186</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2816</v>
+        <v>-0.9866</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1573</v>
+        <v>-0.8139</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0389</v>
+        <v>0.3835</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1184</v>
+        <v>-1.1974</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0575</v>
+        <v>0.2458</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2208</v>
+        <v>0.0351</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1632</v>
+        <v>0.2107</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7335</v>
+        <v>1.0064</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5928</v>
+        <v>0.0075</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1406</v>
+        <v>0.9988</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8713</v>
+        <v>-0.6258</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8913</v>
+        <v>-1.235</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7626</v>
+        <v>0.6092</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4013</v>
+        <v>-0.8292</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1037</v>
+        <v>-1.5021</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.505</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1162</v>
+        <v>-0.9142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8794</v>
+        <v>-1.0054</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2368</v>
+        <v>0.0912</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5174</v>
+        <v>0.0849</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7756</v>
+        <v>-0.4967</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7418</v>
+        <v>0.5816</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="Q8" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4374</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.2073</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.4728</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.2321</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.2832</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.2249</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.0584</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.4189</v>
-      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9107</v>
+        <v>-0.7855</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6612</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2495</v>
+        <v>-0.1902</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3032</v>
@@ -1156,13 +1156,13 @@
         <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2317</v>
+        <v>-0.1065</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>-0.0659</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9873</v>
+        <v>-1.1489</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5372</v>
+        <v>0.6434</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5499000000000001</v>
+        <v>-1.7923</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8292</v>
+        <v>-0.4013</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5021</v>
+        <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.505</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9142</v>
+        <v>1.1162</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0054</v>
+        <v>0.8794</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0912</v>
+        <v>0.2368</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0849</v>
+        <v>-1.5174</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4967</v>
+        <v>-0.7756</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5816</v>
+        <v>-0.7418</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5688</v>
+        <v>-0.5608</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.775</v>
+        <v>-0.4728</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2062</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V10" t="n">
+        <v>-1.4189</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.1786</v>
-      </c>
       <c r="X10" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0213</v>
+        <v>-1.6803</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1311</v>
+        <v>-1.7902</v>
       </c>
       <c r="F11" t="n">
         <v>0.1098</v>
@@ -1312,10 +1312,10 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3952</v>
+        <v>-0.0543</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8681</v>
+        <v>-0.5272</v>
       </c>
       <c r="U11" t="n">
         <v>0.4729</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.5076</v>
+        <v>9.495699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.056</v>
+        <v>2.0441</v>
       </c>
       <c r="F12" t="n">
         <v>7.4517</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4866</v>
+        <v>1.486600000000001</v>
       </c>
       <c r="H12" t="n">
         <v>0.5669999999999995</v>
@@ -1369,7 +1369,7 @@
         <v>4.691000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>2.299</v>
+        <v>2.299000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-5.5035</v>
@@ -1381,7 +1381,7 @@
         <v>-1.3795</v>
       </c>
       <c r="P12" t="n">
-        <v>5.133699999999999</v>
+        <v>5.1337</v>
       </c>
       <c r="Q12" t="n">
         <v>-8.213799999999999</v>
@@ -1390,16 +1390,16 @@
         <v>13.3473</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2521</v>
+        <v>0.7359999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.5272</v>
+        <v>-2.5394</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2753</v>
+        <v>3.2752</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1394</v>
+        <v>2.139400000000001</v>
       </c>
       <c r="W12" t="n">
         <v>5.8067</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5229</v>
+        <v>2.8946</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5002</v>
+        <v>1.8421</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0227</v>
+        <v>1.0525</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4474</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1735</v>
+        <v>-1.2976</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7261</v>
+        <v>0.6318</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8498</v>
+        <v>0.0119</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8103</v>
+        <v>-0.1065</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0395</v>
+        <v>0.1184</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4023</v>
+        <v>-0.6776</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3632</v>
+        <v>-1.191</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.5134</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4594</v>
+        <v>-0.1637</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9995000000000001</v>
+        <v>-0.5619</v>
       </c>
       <c r="U13" t="n">
-        <v>0.46</v>
+        <v>0.3983</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5893</v>
+        <v>2.6973</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3491</v>
+        <v>2.5975</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2402</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0282</v>
+        <v>1.7018</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4237</v>
+        <v>1.768</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6045</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6657999999999999</v>
+        <v>1.4474</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2976</v>
+        <v>2.1735</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6318</v>
+        <v>-0.7261</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0119</v>
+        <v>1.8498</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1065</v>
+        <v>1.8103</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1184</v>
+        <v>0.0395</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6776</v>
+        <v>-0.4023</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.191</v>
+        <v>0.3632</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5134</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0301</v>
+        <v>0.6383</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9804</v>
+        <v>0.2673</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0498</v>
+        <v>0.371</v>
       </c>
       <c r="V14" t="n">
-        <v>2.6973</v>
+        <v>-0.5893</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5975</v>
+        <v>-0.3491</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0998</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5538999999999999</v>
+        <v>1.3717</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1251</v>
+        <v>1.0205</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5711000000000001</v>
+        <v>0.3512</v>
       </c>
       <c r="G15" t="n">
         <v>1.2124</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7993</v>
+        <v>0.0184</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3411</v>
+        <v>-0.4457</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4582</v>
+        <v>0.4641</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2965</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1831</v>
+        <v>1.2101</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9882</v>
+        <v>1.5112</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8051</v>
+        <v>-0.3012</v>
       </c>
       <c r="G16" t="n">
         <v>1.1835</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7335</v>
+        <v>0.2935</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.3837</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1733</v>
+        <v>0.6772</v>
       </c>
       <c r="V16" t="n">
         <v>0.3491</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0513</v>
+        <v>-0.4962</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3192</v>
+        <v>-1.2146</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3705</v>
+        <v>0.7184</v>
       </c>
       <c r="G17" t="n">
         <v>1.0245</v>
@@ -1780,13 +1780,13 @@
         <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>1.491</v>
+        <v>0.9435</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.407</v>
+        <v>-0.3024</v>
       </c>
       <c r="U17" t="n">
-        <v>1.898</v>
+        <v>1.2459</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8827</v>
+        <v>-1.4713</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4326</v>
+        <v>-1.5372</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4502</v>
+        <v>0.0659</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7851</v>
@@ -1858,13 +1858,13 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.303</v>
+        <v>0.1085</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2907</v>
+        <v>-0.3953</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0123</v>
+        <v>0.5038</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5893</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9584</v>
+        <v>-2.2732</v>
       </c>
       <c r="E19" t="n">
         <v>-4.0044</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0459</v>
+        <v>1.7311</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4269</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.504</v>
+        <v>0.1811</v>
       </c>
       <c r="T19" t="n">
         <v>-0.283</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.221</v>
+        <v>0.4641</v>
       </c>
       <c r="V19" t="n">
         <v>0.2312</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6957</v>
+        <v>-4.3345</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9335</v>
+        <v>-2.2473</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7622</v>
+        <v>-2.0871</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7868</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1473</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0854</v>
+        <v>-0.3992</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2327</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6456</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3101</v>
+        <v>-4.9196</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.7991</v>
+        <v>-4.5899</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.511</v>
+        <v>-0.3297</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6899</v>
@@ -2092,13 +2092,13 @@
         <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4757</v>
+        <v>-0.0852</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9804</v>
+        <v>-0.7711</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5047</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2965</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.5075</v>
+        <v>-6.3166</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.451600000000003</v>
+        <v>-7.451600000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.056</v>
+        <v>1.1349</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4867</v>
@@ -2170,13 +2170,13 @@
         <v>8.2136</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2521000000000002</v>
+        <v>2.443</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.2753</v>
+        <v>-3.275</v>
       </c>
       <c r="U22" t="n">
-        <v>3.5274</v>
+        <v>5.7182</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1396</v>
